--- a/1.xlsx
+++ b/1.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>招聘类型</t>
   </si>
@@ -83,14 +83,788 @@
     <t>公司福利</t>
   </si>
   <si>
-    <t>应届校园招聘</t>
-  </si>
-  <si>
-    <t>Java研发工程师-校招测试</t>
-  </si>
-  <si>
-    <t>岗位职责：参与核心系统研发，在导师指导下完成模块开发和联调。
-任职要求：计算机相关专业，Java基础扎实，了解数据库。</t>
+    <t>社招全职</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Java-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>开发</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(J14899)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>【公司亮点】</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、业务定位：专注</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ToB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>业务，以云计算</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>SaaS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>模式，提供电商</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ERP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>WMS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>等一体化智能零售解决方案，助力零售企业数字化升级、提升运营效率。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、规模布局：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">2011 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年成立，员工</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">3000 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>人，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">130 + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>网点覆盖</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 400 + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>城市及海外；对接</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 400 + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>平台，融资超</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 4.52 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>亿美元，创国内</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> SaaS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>行业单笔融资纪录。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、行业实力：服务</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 70 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>万</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>电商企业，含</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 80 + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>世界</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 500 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>强、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">500 + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>上市公司；连续</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 5 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年胡润独角兽，市场份额庞大，获多项行业荣誉。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>【岗位亮点】</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、技术实战：直面日处理</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1.38</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>亿单、支撑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1/3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>线上交易履约的高并发分布式场景，参与核心技术方案设计，攻坚订单处理等难点，快速沉淀企业级大规模场景实战能力。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、发展空间：晋升标准清晰量化，每年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>次高频晋升窗口，提供专业与管理双发展路径；从基层、中层到高层管理者、专业专家，发展机会充足，年度新干部晋升率达</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>40%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，发展灵活透明。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>【岗位职责】</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、系统开发与实现：根据产品需求，完成相应模块的开发工作，确保代码质量、可维护性和性能。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、技术问题解决：面对技术问题，能够主动寻找解决方案，与团队成员共同攻克难关，保障项目顺利进行。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、代码审查与优化：参与代码审查，提出改进意见，持续优化代码质量，提升系统稳定性和效率。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、技术文档编写：负责相关技术文档的编写与更新，确保团队内外信息同步，便于后续维护与扩展。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>【岗位要求】</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、统招本科及以上学历，计算机相关专业，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">1-3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> Java </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>开发经验。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、熟练掌握</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> Java </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>及</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> Spring Boot </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>等主流框架，精通</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> SQL </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>与数据库开发，熟悉</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> Linux </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>与</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> Git</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、具备扎实的逻辑思维、问题解决能力，学习与沟通能力良好，能快速适应新技术；有责任心与团队协作意识，主动担当。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、有微服务</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>分布式、大型互联网项目经验、开源项目贡献经历，或在技术社区有活跃表现者优先。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
   </si>
   <si>
     <t>境内岗位</t>
@@ -99,90 +873,52 @@
     <t>Java</t>
   </si>
   <si>
-    <t>在校/应届</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1-3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年</t>
+    </r>
   </si>
   <si>
     <t>本科</t>
   </si>
   <si>
-    <t>10k</t>
-  </si>
-  <si>
-    <t>15k</t>
-  </si>
-  <si>
-    <t>无</t>
-  </si>
-  <si>
-    <t>Java Spring MySQL</t>
-  </si>
-  <si>
-    <t>北京海淀区中国外文大厦A座3层</t>
-  </si>
-  <si>
-    <t>2026</t>
-  </si>
-  <si>
-    <t>2026-06-30</t>
-  </si>
-  <si>
-    <t>导师带教 晋升机会 定期团建</t>
-  </si>
-  <si>
-    <t>实习生招聘</t>
-  </si>
-  <si>
-    <t>Java工程师-实习测试</t>
-  </si>
-  <si>
-    <t>岗位职责：参与Java后端模块开发、单元测试和文档维护。
-任职要求：每周稳定到岗，熟悉Java基础和常用框架。</t>
-  </si>
-  <si>
-    <t>250</t>
-  </si>
-  <si>
-    <t>300</t>
-  </si>
-  <si>
-    <t>3个月</t>
-  </si>
-  <si>
-    <t>5天</t>
-  </si>
-  <si>
-    <t>实习证明 导师带教 弹性工作</t>
-  </si>
-  <si>
-    <t>兼职招聘</t>
-  </si>
-  <si>
-    <t>Java兼职讲师-测试</t>
-  </si>
-  <si>
-    <t>岗位职责：负责Java课程辅导、代码答疑和学习进度跟进。
-任职要求：Java基础扎实，有授课或辅导经验优先。</t>
-  </si>
-  <si>
-    <t>不限</t>
-  </si>
-  <si>
-    <t>80</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>元/时</t>
-  </si>
-  <si>
-    <t>日结</t>
-  </si>
-  <si>
-    <t>2026-05-31</t>
-  </si>
-  <si>
-    <t>时间灵活 远程协作</t>
+    <t>12k</t>
+  </si>
+  <si>
+    <t>20k</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>13</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>个月</t>
+    </r>
+  </si>
+  <si>
+    <t>Java Spring Mysql</t>
   </si>
 </sst>
 </file>
@@ -195,10 +931,15 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -658,154 +1399,159 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1231,11 +1977,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3"/>
+  <dimension ref="A1:R2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1"/>
   <cols>
+    <col min="1" max="1" width="25.3333333333333" customWidth="1"/>
     <col min="2" max="2" width="39" customWidth="1"/>
+    <col min="3" max="3" width="27.5" customWidth="1"/>
     <col min="6" max="6" width="24.5833333333333" customWidth="1"/>
+    <col min="12" max="12" width="29.4166666666667" customWidth="1"/>
+    <col min="13" max="13" width="18.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
@@ -1294,26 +2044,26 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18">
-      <c r="A2" t="s">
+    <row r="2" ht="409.5" spans="1:18">
+      <c r="A2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E2" t="s">
         <v>22</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H2" t="s">
@@ -1322,144 +2072,11 @@
       <c r="I2" t="s">
         <v>26</v>
       </c>
-      <c r="J2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="J2" s="2" t="s">
         <v>27</v>
       </c>
       <c r="L2" t="s">
         <v>28</v>
-      </c>
-      <c r="M2" t="s">
-        <v>29</v>
-      </c>
-      <c r="N2" t="s">
-        <v>30</v>
-      </c>
-      <c r="O2" t="s">
-        <v>27</v>
-      </c>
-      <c r="P2" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>31</v>
-      </c>
-      <c r="R2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18">
-      <c r="A3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I3" t="s">
-        <v>37</v>
-      </c>
-      <c r="J3" t="s">
-        <v>27</v>
-      </c>
-      <c r="K3" t="s">
-        <v>27</v>
-      </c>
-      <c r="L3" t="s">
-        <v>28</v>
-      </c>
-      <c r="M3" t="s">
-        <v>29</v>
-      </c>
-      <c r="N3" t="s">
-        <v>27</v>
-      </c>
-      <c r="O3" t="s">
-        <v>38</v>
-      </c>
-      <c r="P3" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>27</v>
-      </c>
-      <c r="R3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18">
-      <c r="A4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" t="s">
-        <v>44</v>
-      </c>
-      <c r="G4" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4" t="s">
-        <v>45</v>
-      </c>
-      <c r="I4" t="s">
-        <v>46</v>
-      </c>
-      <c r="J4" t="s">
-        <v>47</v>
-      </c>
-      <c r="K4" t="s">
-        <v>48</v>
-      </c>
-      <c r="L4" t="s">
-        <v>28</v>
-      </c>
-      <c r="M4" t="s">
-        <v>27</v>
-      </c>
-      <c r="N4" t="s">
-        <v>27</v>
-      </c>
-      <c r="O4" t="s">
-        <v>27</v>
-      </c>
-      <c r="P4" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>49</v>
-      </c>
-      <c r="R4" t="s">
-        <v>50</v>
       </c>
     </row>
   </sheetData>
